--- a/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0003T0006Z000C1N28_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0003T0006Z000C1N28_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>75.17404491013178</v>
+        <v>12.21578229789642</v>
       </c>
       <c r="D2" t="n">
-        <v>8.752021984423827</v>
+        <v>1.422203572468872</v>
       </c>
       <c r="E2" t="n">
-        <v>11.66361344695343</v>
+        <v>1.895337185129933</v>
       </c>
       <c r="F2" t="n">
-        <v>19.19305551476086</v>
+        <v>3.11887152114864</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>45.53670085709864</v>
+        <v>7.39971388927853</v>
       </c>
       <c r="D3" t="n">
-        <v>46.34122494827834</v>
+        <v>7.53044905409523</v>
       </c>
       <c r="E3" t="n">
-        <v>11.66361344695343</v>
+        <v>1.895337185129933</v>
       </c>
       <c r="F3" t="n">
-        <v>19.19305551476086</v>
+        <v>3.11887152114864</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>44.42248789338088</v>
+        <v>7.218654282674392</v>
       </c>
       <c r="D4" t="n">
-        <v>44.59093589375836</v>
+        <v>7.246027082735734</v>
       </c>
       <c r="E4" t="n">
-        <v>11.66361344695343</v>
+        <v>1.895337185129933</v>
       </c>
       <c r="F4" t="n">
-        <v>19.19305551476086</v>
+        <v>3.11887152114864</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>64.69053868911728</v>
+        <v>10.51221253698156</v>
       </c>
       <c r="D5" t="n">
-        <v>63.82494663587842</v>
+        <v>10.37155382833024</v>
       </c>
       <c r="E5" t="n">
-        <v>11.66361344695343</v>
+        <v>1.895337185129933</v>
       </c>
       <c r="F5" t="n">
-        <v>19.19305551476086</v>
+        <v>3.11887152114864</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>59.03296474215956</v>
+        <v>9.592856770600928</v>
       </c>
       <c r="D6" t="n">
-        <v>58.18311082269972</v>
+        <v>9.454755508688706</v>
       </c>
       <c r="E6" t="n">
-        <v>11.66361344695343</v>
+        <v>1.895337185129933</v>
       </c>
       <c r="F6" t="n">
-        <v>19.19305551476086</v>
+        <v>3.11887152114864</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
